--- a/diseases/d114/1975-1979.xlsx
+++ b/diseases/d114/1975-1979.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>14</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>20</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>16</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>12</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>14</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>30</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>45</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>37</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>19</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>22</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>15</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>15</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>35</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>18</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>15</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>16</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>13</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>24</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>49</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>25</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>27</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>30</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>19</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>32</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>27</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>31</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>13</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>14</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>21</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>32</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>38</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>40</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>27</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>13</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14519,9 +14414,6 @@
       </c>
       <c r="O72" t="n">
         <v>28</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>

--- a/diseases/d114/1975-1979.xlsx
+++ b/diseases/d114/1975-1979.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,19 +751,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1977-01-01</t>
+          <t>1975-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1977-01</t>
+          <t>1975-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>3457</v>
       </c>
       <c r="O2" t="n">
-        <v>14</v>
+        <v>3457</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -907,38 +907,38 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1977-01-01</t>
+          <t>1975-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1977-01</t>
+          <t>1975-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>3457</v>
       </c>
       <c r="O3" t="n">
-        <v>14</v>
+        <v>3457</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1141,19 +1141,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1977-02-01</t>
+          <t>1976-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1977-02</t>
+          <t>1976-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>2929</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>2929</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1200,42 +1200,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1977-02-01</t>
+          <t>1976-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1977-02</t>
+          <t>1976-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>2929</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>2929</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1434,42 +1434,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1977-03-01</t>
+          <t>1977-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1977-03</t>
+          <t>1977-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>4228</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>4228</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -1590,42 +1590,42 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1687,38 +1687,38 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1977-03-01</t>
+          <t>1977-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1977-03</t>
+          <t>1977-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>4228</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>4228</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1824,42 +1824,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1977-04-01</t>
+          <t>1977-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1977-04</t>
+          <t>1977-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2077,19 +2082,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1977-04-01</t>
+          <t>1977-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1977-04</t>
+          <t>1977-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2191,7 +2196,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2204,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2311,19 +2321,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1977-05-01</t>
+          <t>1977-02-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1977-05</t>
+          <t>1977-02</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2347,7 +2357,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2365,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2467,19 +2482,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1977-05-01</t>
+          <t>1977-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1977-05</t>
+          <t>1977-02</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2581,7 +2596,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2604,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2701,19 +2721,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1977-06-01</t>
+          <t>1977-03-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1977-06</t>
+          <t>1977-03</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2737,7 +2757,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2857,19 +2882,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1977-06-01</t>
+          <t>1977-03-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1977-06</t>
+          <t>1977-03</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2971,7 +2996,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3091,19 +3121,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1977-07-01</t>
+          <t>1977-04-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1977-07</t>
+          <t>1977-04</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3127,7 +3157,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3247,19 +3282,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1977-07-01</t>
+          <t>1977-04-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1977-07</t>
+          <t>1977-04</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3361,7 +3396,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3481,19 +3521,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1977-08-01</t>
+          <t>1977-05-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1977-08</t>
+          <t>1977-05</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3517,7 +3557,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3637,19 +3682,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1977-08-01</t>
+          <t>1977-05-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1977-08</t>
+          <t>1977-05</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3751,7 +3796,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3871,19 +3921,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1977-09-01</t>
+          <t>1977-06-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1977-09</t>
+          <t>1977-06</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3907,7 +3957,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4027,19 +4082,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1977-09-01</t>
+          <t>1977-06-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1977-09</t>
+          <t>1977-06</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4141,7 +4196,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4204,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4261,19 +4321,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1977-10-01</t>
+          <t>1977-07-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1977-10</t>
+          <t>1977-07</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4297,7 +4357,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4365,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4417,19 +4482,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1977-10-01</t>
+          <t>1977-07-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1977-10</t>
+          <t>1977-07</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4531,7 +4596,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4604,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4651,19 +4721,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1977-11-01</t>
+          <t>1977-08-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1977-11</t>
+          <t>1977-08</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4687,7 +4757,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4807,19 +4882,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1977-11-01</t>
+          <t>1977-08-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1977-11</t>
+          <t>1977-08</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="O23" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -4921,7 +4996,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5041,19 +5121,19 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1977-12-01</t>
+          <t>1977-09-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1977-12</t>
+          <t>1977-09</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5077,7 +5157,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5197,19 +5282,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1977-12-01</t>
+          <t>1977-09-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1977-12</t>
+          <t>1977-09</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5311,7 +5396,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5431,19 +5521,19 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1978-01-01</t>
+          <t>1977-10-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1978-01</t>
+          <t>1977-10</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5467,7 +5557,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5587,19 +5682,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1978-01-01</t>
+          <t>1977-10-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1978-01</t>
+          <t>1977-10</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5701,7 +5796,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5821,19 +5921,19 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1978-02-01</t>
+          <t>1977-11-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1978-02</t>
+          <t>1977-11</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="O28" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5857,7 +5957,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5865,17 +5965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5977,19 +6082,19 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1978-02-01</t>
+          <t>1977-11-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1978-02</t>
+          <t>1977-11</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="O29" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -6091,7 +6196,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6099,17 +6204,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6211,19 +6321,19 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1978-03-01</t>
+          <t>1977-12-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1978-03</t>
+          <t>1977-12</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6247,7 +6357,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6255,17 +6365,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6367,19 +6482,19 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1978-03-01</t>
+          <t>1977-12-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1978-03</t>
+          <t>1977-12</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6481,7 +6596,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6489,17 +6604,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6571,12 +6691,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6601,19 +6721,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1978-04-01</t>
+          <t>1978-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1978-04</t>
+          <t>1978-01</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>15</v>
+        <v>6693</v>
       </c>
       <c r="O32" t="n">
-        <v>15</v>
+        <v>6693</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6622,12 +6742,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -6647,7 +6767,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -6660,42 +6780,42 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6727,12 +6847,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6757,38 +6877,38 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1978-04-01</t>
+          <t>1978-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1978-04</t>
+          <t>1978-01</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>15</v>
+        <v>6693</v>
       </c>
       <c r="O33" t="n">
-        <v>15</v>
+        <v>6693</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -6798,12 +6918,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -6813,7 +6933,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -6848,17 +6968,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6881,7 +7001,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -6894,42 +7014,42 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6991,19 +7111,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1978-05-01</t>
+          <t>1978-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1978-05</t>
+          <t>1978-01</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7027,7 +7147,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -7035,17 +7155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7147,19 +7272,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1978-05-01</t>
+          <t>1978-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1978-05</t>
+          <t>1978-01</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7261,7 +7386,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7269,17 +7394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7381,19 +7511,19 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1978-06-01</t>
+          <t>1978-02-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1978-06</t>
+          <t>1978-02</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="O36" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -7417,7 +7547,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7537,19 +7672,19 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1978-06-01</t>
+          <t>1978-02-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1978-06</t>
+          <t>1978-02</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="O37" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -7651,7 +7786,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7771,19 +7911,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1978-07-01</t>
+          <t>1978-03-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1978-07</t>
+          <t>1978-03</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O38" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7807,7 +7947,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7955,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7927,19 +8072,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1978-07-01</t>
+          <t>1978-03-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1978-07</t>
+          <t>1978-03</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O39" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -8041,7 +8186,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8194,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8161,19 +8311,19 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1978-08-01</t>
+          <t>1978-04-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1978-08</t>
+          <t>1978-04</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="O40" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -8197,7 +8347,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8355,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8317,19 +8472,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1978-08-01</t>
+          <t>1978-04-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1978-08</t>
+          <t>1978-04</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="O41" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8431,7 +8586,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8551,19 +8711,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1978-09-01</t>
+          <t>1978-05-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1978-09</t>
+          <t>1978-05</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O42" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8587,7 +8747,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8707,19 +8872,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1978-09-01</t>
+          <t>1978-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1978-09</t>
+          <t>1978-05</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O43" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -8821,7 +8986,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +8994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8941,19 +9111,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1978-10-01</t>
+          <t>1978-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1978-10</t>
+          <t>1978-06</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O44" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8977,7 +9147,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9097,19 +9272,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1978-10-01</t>
+          <t>1978-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1978-10</t>
+          <t>1978-06</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O45" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9211,7 +9386,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9331,19 +9511,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1978-11-01</t>
+          <t>1978-07-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1978-11</t>
+          <t>1978-07</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="O46" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9367,7 +9547,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9487,19 +9672,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1978-11-01</t>
+          <t>1978-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1978-11</t>
+          <t>1978-07</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="O47" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9601,7 +9786,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9721,19 +9911,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1978-12-01</t>
+          <t>1978-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1978-12</t>
+          <t>1978-08</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="O48" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9757,7 +9947,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9955,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9877,19 +10072,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1978-12-01</t>
+          <t>1978-08-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1978-12</t>
+          <t>1978-08</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="O49" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9991,7 +10186,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,17 +10194,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10111,19 +10311,19 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1978-09-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1979-01</t>
+          <t>1978-09</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O50" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -10147,7 +10347,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10155,17 +10355,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10267,19 +10472,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1978-09-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1979-01</t>
+          <t>1978-09</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O51" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -10381,7 +10586,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10389,17 +10594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10501,12 +10711,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1979-02-01</t>
+          <t>1978-10-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1979-02</t>
+          <t>1978-10</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -10537,7 +10747,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10545,17 +10755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10657,12 +10872,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1979-02-01</t>
+          <t>1978-10-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1979-02</t>
+          <t>1978-10</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10771,7 +10986,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10779,17 +10994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10891,19 +11111,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1979-03-01</t>
+          <t>1978-11-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1979-03</t>
+          <t>1978-11</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O54" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10927,7 +11147,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10935,17 +11155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11047,19 +11272,19 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1979-03-01</t>
+          <t>1978-11-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1979-03</t>
+          <t>1978-11</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O55" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -11161,7 +11386,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -11169,17 +11394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11281,19 +11511,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1979-04-01</t>
+          <t>1978-12-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1979-04</t>
+          <t>1978-12</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O56" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11317,7 +11547,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11325,17 +11555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11437,19 +11672,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1979-04-01</t>
+          <t>1978-12-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1979-04</t>
+          <t>1978-12</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O57" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11551,7 +11786,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -11559,17 +11794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -11641,12 +11881,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11671,19 +11911,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1979-05-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1979-05</t>
+          <t>1979-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>7420</v>
       </c>
       <c r="O58" t="n">
-        <v>14</v>
+        <v>7420</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11692,12 +11932,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -11717,7 +11957,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11730,42 +11970,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11797,12 +12037,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11827,38 +12067,38 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1979-05-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1979-05</t>
+          <t>1979-01</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>14</v>
+        <v>7420</v>
       </c>
       <c r="O59" t="n">
-        <v>14</v>
+        <v>7420</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11868,12 +12108,12 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -11883,7 +12123,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11918,17 +12158,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11951,7 +12191,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D108_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -11964,42 +12204,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12061,19 +12301,19 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1979-06-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1979-06</t>
+          <t>1979-01</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="O60" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12097,7 +12337,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12105,17 +12345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12217,19 +12462,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1979-06-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1979-06</t>
+          <t>1979-01</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12331,7 +12576,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12339,17 +12584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12451,19 +12701,19 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1979-07-01</t>
+          <t>1979-02-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1979-07</t>
+          <t>1979-02</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O62" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12487,7 +12737,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12495,17 +12745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12607,19 +12862,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1979-07-01</t>
+          <t>1979-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1979-07</t>
+          <t>1979-02</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O63" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12721,7 +12976,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12729,17 +12984,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12841,19 +13101,19 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1979-08-01</t>
+          <t>1979-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1979-08</t>
+          <t>1979-03</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="O64" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12877,7 +13137,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12885,17 +13145,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -12997,19 +13262,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1979-08-01</t>
+          <t>1979-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1979-08</t>
+          <t>1979-03</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="O65" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13111,7 +13376,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13119,17 +13384,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13231,19 +13501,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1979-09-01</t>
+          <t>1979-04-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1979-09</t>
+          <t>1979-04</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="O66" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13267,7 +13537,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13275,17 +13545,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13387,19 +13662,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1979-09-01</t>
+          <t>1979-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1979-09</t>
+          <t>1979-04</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="O67" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13501,7 +13776,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13509,17 +13784,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13621,19 +13901,19 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1979-10-01</t>
+          <t>1979-05-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1979-10</t>
+          <t>1979-05</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="O68" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13657,7 +13937,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13665,17 +13945,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13777,19 +14062,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1979-10-01</t>
+          <t>1979-05-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1979-10</t>
+          <t>1979-05</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="O69" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -13891,7 +14176,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13899,17 +14184,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14011,19 +14301,19 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1979-11-01</t>
+          <t>1979-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1979-11</t>
+          <t>1979-06</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="O70" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14047,7 +14337,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14055,17 +14345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14167,19 +14462,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1979-11-01</t>
+          <t>1979-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1979-11</t>
+          <t>1979-06</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="O71" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14281,7 +14576,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14289,17 +14584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14401,19 +14701,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1979-12-01</t>
+          <t>1979-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1979-12</t>
+          <t>1979-07</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O72" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14437,7 +14737,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14445,17 +14745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14557,19 +14862,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1979-12-01</t>
+          <t>1979-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1979-12</t>
+          <t>1979-07</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O73" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -14671,7 +14976,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14679,55 +14984,2060 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1979-08-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1979-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>38</v>
+      </c>
+      <c r="O74" t="n">
+        <v>38</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1979-08-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1979-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>38</v>
+      </c>
+      <c r="O75" t="n">
+        <v>38</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
         <v>1</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV73" t="inlineStr">
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW73" t="inlineStr">
+      <c r="AW75" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AX75" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
+      <c r="AY75" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA73" t="inlineStr">
+      <c r="BA75" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB73" t="inlineStr">
+      <c r="BB75" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC73" t="inlineStr">
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1979-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1979-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>40</v>
+      </c>
+      <c r="O76" t="n">
+        <v>40</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1979-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1979-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>40</v>
+      </c>
+      <c r="O77" t="n">
+        <v>40</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1979-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1979-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>27</v>
+      </c>
+      <c r="O78" t="n">
+        <v>27</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1979-10-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1979-10</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>27</v>
+      </c>
+      <c r="O79" t="n">
+        <v>27</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1979-11-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1979-11</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>13</v>
+      </c>
+      <c r="O80" t="n">
+        <v>13</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1979-11-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1979-11</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>13</v>
+      </c>
+      <c r="O81" t="n">
+        <v>13</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1979-12-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1979-12</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>28</v>
+      </c>
+      <c r="O82" t="n">
+        <v>28</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1979-12-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1979-12</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>28</v>
+      </c>
+      <c r="O83" t="n">
+        <v>28</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -14778,7 +17088,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1977-01-01</t>
+          <t>1975-01-01</t>
         </is>
       </c>
     </row>
@@ -14849,7 +17159,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -14859,7 +17169,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -14879,7 +17189,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -14889,7 +17199,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -14911,7 +17221,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>853</v>
+        <v>25580</v>
       </c>
     </row>
     <row r="16">
